--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67591_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67591_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8f717cdaa92c4200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rab52aed61e244dab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.4872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.8428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67591_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67591_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rab52aed61e244dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfd1802edd3194bcd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.1620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     95.7491</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.5742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.7591</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.3777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.3753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.2041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.1620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.2041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.1864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.1864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.1072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.0121</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    515.0394</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.1146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.8169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.2399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.6817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.3337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.7376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.0345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.4431</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.5552</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.0345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.6355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.2462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.2462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4969</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7808</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,27 +984,27 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     25.7870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     26.4470</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>22/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.4470</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>21/08/2026</x:t>
         </x:is>
       </x:c>
@@ -294,28 +1014,328 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     27.7970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.4872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.3777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     27.1170</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.4872</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/08/2026</x:t>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.1408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.8360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.3497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.3497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -330,292 +1350,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.6187</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.8979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.1170</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.1170</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7970</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7970</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.4872</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.8979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.8979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.8979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.8979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.6187</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.6187</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.6187</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.3497</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.3497</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.3497</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.0910</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.0910</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
+          <x:t>29/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -630,21 +1365,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.8428</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>28/07/2026</x:t>
         </x:is>
       </x:c>
@@ -3174,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    262.9541</x:v>
+        <x:v>    215.9885</x:v>
       </x:c>
     </x:row>
     <x:row>
